--- a/收集表/115_10_排課需求收集表.xlsx
+++ b/收集表/115_10_排課需求收集表.xlsx
@@ -1334,8 +1334,8 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
@@ -3548,7 +3548,7 @@
           <t>整天</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="35" t="inlineStr">
         <is>
           <t>同科分散</t>
         </is>
@@ -3565,7 +3565,7 @@
           <t>1年11班</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="35" t="inlineStr">
         <is>
           <t>間隔天數</t>
         </is>
@@ -4751,84 +4751,84 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>3 盡量</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>同科分散</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>所有科任</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>同一班同一科一天最多 1 次（連堂算 1 次）</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="35" t="inlineStr">
         <is>
           <t>避免同一天上兩次同科</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>3 盡量</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>間隔天數</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="35" t="inlineStr">
         <is>
           <t>自然</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>同一班自然各次上課至少隔 1 天（例：星期一上連堂，原班那節排星期三以後）</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="35" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="35" t="inlineStr">
         <is>
           <t>Bing 2026-10-21：原班那節要不同天，最好差一天</t>
         </is>
@@ -11898,97 +11898,241 @@
     <row r="7" ht="17.15" customHeight="1" s="36">
       <c r="A7" s="44" t="inlineStr">
         <is>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>不上課</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G7" s="44" t="inlineStr">
+        <is>
+          <t>星期三下午半天</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.15" customHeight="1" s="36">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
           <t>一、二年級</t>
         </is>
       </c>
-      <c r="B7" s="52" t="n"/>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>下午</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D8" s="44" t="inlineStr">
         <is>
           <t>不上課</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr">
+      <c r="E8" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F8" s="44" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" s="44" t="inlineStr">
-        <is>
-          <t>請填星期（沿用目前作息）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.15" customHeight="1" s="36">
-      <c r="A8" s="44" t="n"/>
-      <c r="B8" s="52" t="n"/>
-      <c r="C8" s="44" t="n"/>
-      <c r="D8" s="44" t="inlineStr">
-        <is>
-          <t>（學校共同課）</t>
-        </is>
-      </c>
-      <c r="E8" s="44" t="n"/>
-      <c r="F8" s="44" t="n"/>
       <c r="G8" s="44" t="inlineStr">
         <is>
-          <t>請補填</t>
+          <t>低年級只有星期二整天</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="36">
-      <c r="A9" s="44" t="n"/>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="44" t="n"/>
-      <c r="D9" s="44" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="44" t="n"/>
-      <c r="G9" s="44" t="n"/>
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>一、二年級</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>不上課</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>低年級只有星期二整天</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="36">
-      <c r="A10" s="44" t="n"/>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="44" t="n"/>
-      <c r="D10" s="44" t="n"/>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="44" t="n"/>
-      <c r="G10" s="44" t="n"/>
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>一、二年級</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>不上課</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>低年級只有星期二整天</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="36">
-      <c r="A11" s="44" t="n"/>
-      <c r="B11" s="52" t="n"/>
-      <c r="C11" s="44" t="n"/>
-      <c r="D11" s="44" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="44" t="n"/>
-      <c r="G11" s="44" t="n"/>
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>一、二年級</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>不上課</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>低年級只有星期二整天</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="36">
-      <c r="A12" s="44" t="n"/>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="44" t="n"/>
-      <c r="D12" s="44" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="44" t="n"/>
-      <c r="G12" s="44" t="n"/>
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>三、四年級</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>不上課</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>中年級星期一、二、四整天</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="36">
       <c r="A13" s="44" t="n"/>
       <c r="B13" s="52" t="n"/>
       <c r="C13" s="44" t="n"/>
-      <c r="D13" s="44" t="n"/>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>（學校共同課）</t>
+        </is>
+      </c>
       <c r="E13" s="44" t="n"/>
       <c r="F13" s="44" t="n"/>
-      <c r="G13" s="44" t="n"/>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>請補填</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="36">
       <c r="A14" s="44" t="n"/>

--- a/收集表/115_10_排課需求收集表.xlsx
+++ b/收集表/115_10_排課需求收集表.xlsx
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H20" s="35" t="inlineStr">
         <is>
-          <t>避免同一天上兩次同科</t>
+          <t>避免同一天上兩次同科（Bing 2026-10-21 確認保留）</t>
         </is>
       </c>
     </row>

--- a/收集表/115_10_排課需求收集表.xlsx
+++ b/收集表/115_10_排課需求收集表.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職務限制" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級教室" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老師需求" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老師需求單" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="節數檢核" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選項" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級需求" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老師需求單" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="節數檢核" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選項" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'規則表'!$3:$3</definedName>
@@ -29,7 +30,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'職務限制'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'班級教室'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'老師需求'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'節數檢核'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'節數檢核'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1127,6 +1128,68 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="36" min="1" max="1"/>
+    <col width="14" customWidth="1" style="36" min="2" max="2"/>
+    <col width="14" customWidth="1" style="36" min="3" max="3"/>
+    <col width="10" customWidth="1" style="36" min="4" max="4"/>
+    <col width="36" customWidth="1" style="36" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>8-2. 班級需求（導師的需求）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>一列＝一個班級不想排科任的時段。班級可填單一班（3年1班）或整個年級（一、二年級）；星期可填一～五、「每天」或「二、四擇一」（系統挑一天）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>班級</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>節次／時段</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>程度</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>原因（選填）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1350,7 +1413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3073,7 +3136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3580,6 +3643,11 @@
       <c r="B13" s="35" t="inlineStr">
         <is>
           <t>1年12班</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>班級不排時段</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="35" min="1" max="1"/>
@@ -4831,6 +4899,90 @@
       <c r="H21" s="35" t="inlineStr">
         <is>
           <t>Bing 2026-10-21：原班那節要不同天，最好差一天</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2 必須</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>班級不排時段</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>個別班級</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>導師勾「必須」的時段不排科任（依「班級需求」頁；可填「每天」「二、四擇一」）</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>導師需要自己上課的時段</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3 盡量</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>班級不排時段</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>個別班級</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>導師勾「希望」的時段盡量不排科任（依「班級需求」頁）</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>導師的希望</t>
         </is>
       </c>
     </row>
